--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3BCF0B4-5BF7-4AAE-889B-FACF81F6C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26A4EDE-20CC-4D0A-A18D-2556469518EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1100,9 +1100,9 @@
     <col min="10" max="10" width="14.796875" customWidth="1"/>
     <col min="11" max="11" width="15.73046875" customWidth="1"/>
     <col min="12" max="12" width="14.796875" customWidth="1"/>
-    <col min="19" max="19" width="14.86328125" customWidth="1"/>
-    <col min="20" max="20" width="12.19921875" customWidth="1"/>
+    <col min="19" max="20" width="26.9296875" customWidth="1"/>
     <col min="21" max="21" width="11.59765625" customWidth="1"/>
+    <col min="22" max="22" width="21.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.45">

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26A4EDE-20CC-4D0A-A18D-2556469518EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26646D90-CB2F-4DB4-9815-E46B873BD90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="243">
   <si>
     <t>Update Terakhir</t>
   </si>
@@ -94,7 +94,7 @@
     <t>--- (Tidak Ada / Kosong) ---</t>
   </si>
   <si>
-    <t>2026-09-10 19:02:53</t>
+    <t>2026-09-14 12:26:04</t>
   </si>
   <si>
     <t>005/BSS-JOB/WS/V/2026</t>
@@ -154,10 +154,13 @@
     <t>008/BSS-JOB/WS/VII/2026</t>
   </si>
   <si>
-    <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+    <t>Kendaraan Operasional Pendukung Inspeksi Supporting Equipment Kegiatan Wellservices</t>
   </si>
   <si>
     <t>09 Jul 2026</t>
+  </si>
+  <si>
+    <t>4500011681</t>
   </si>
   <si>
     <t>06 Jul 2026</t>
@@ -1088,21 +1091,8 @@
   <dimension ref="A1:AF47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.53125" customWidth="1"/>
-    <col min="3" max="3" width="17.9296875" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" customWidth="1"/>
-    <col min="5" max="5" width="17.3984375" customWidth="1"/>
-    <col min="6" max="6" width="19.46484375" customWidth="1"/>
-    <col min="7" max="7" width="14.265625" customWidth="1"/>
-    <col min="8" max="8" width="16.46484375" customWidth="1"/>
-    <col min="9" max="9" width="15.1328125" customWidth="1"/>
-    <col min="10" max="10" width="14.796875" customWidth="1"/>
-    <col min="11" max="11" width="15.73046875" customWidth="1"/>
-    <col min="12" max="12" width="14.796875" customWidth="1"/>
-    <col min="19" max="20" width="26.9296875" customWidth="1"/>
-    <col min="21" max="21" width="11.59765625" customWidth="1"/>
-    <col min="22" max="22" width="21.73046875" customWidth="1"/>
+    <col min="21" max="21" width="12.33203125" customWidth="1"/>
+    <col min="22" max="22" width="20.06640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.45">
@@ -1492,8 +1482,11 @@
       <c r="H5" t="s">
         <v>32</v>
       </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K5" t="s">
         <v>10</v>
@@ -1520,7 +1513,7 @@
         <v>17</v>
       </c>
       <c r="S5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T5" t="s">
         <v>43</v>
@@ -1528,8 +1521,14 @@
       <c r="U5" t="s">
         <v>45</v>
       </c>
+      <c r="V5" t="s">
+        <v>46</v>
+      </c>
       <c r="W5" t="s">
         <v>44</v>
+      </c>
+      <c r="X5" t="s">
+        <v>46</v>
       </c>
       <c r="Y5" t="s">
         <v>19</v>
@@ -1555,7 +1554,7 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1564,7 +1563,7 @@
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
@@ -1573,13 +1572,13 @@
         <v>30</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H6" t="s">
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
@@ -1606,19 +1605,19 @@
         <v>17</v>
       </c>
       <c r="S6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U6" t="s">
+        <v>51</v>
+      </c>
+      <c r="V6" t="s">
+        <v>49</v>
+      </c>
+      <c r="W6" t="s">
         <v>50</v>
-      </c>
-      <c r="V6" t="s">
-        <v>48</v>
-      </c>
-      <c r="W6" t="s">
-        <v>49</v>
       </c>
       <c r="Y6" t="s">
         <v>19</v>
@@ -1644,7 +1643,7 @@
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1653,25 +1652,25 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" t="s">
         <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
@@ -1698,16 +1697,16 @@
         <v>17</v>
       </c>
       <c r="S7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y7" t="s">
         <v>19</v>
@@ -1733,7 +1732,7 @@
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1742,22 +1741,22 @@
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" t="s">
         <v>32</v>
       </c>
       <c r="J8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K8" t="s">
         <v>10</v>
@@ -1784,16 +1783,16 @@
         <v>17</v>
       </c>
       <c r="S8" t="s">
+        <v>64</v>
+      </c>
+      <c r="T8" t="s">
+        <v>60</v>
+      </c>
+      <c r="U8" t="s">
         <v>63</v>
       </c>
-      <c r="T8" t="s">
-        <v>59</v>
-      </c>
-      <c r="U8" t="s">
-        <v>62</v>
-      </c>
       <c r="W8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y8" t="s">
         <v>19</v>
@@ -1819,7 +1818,7 @@
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1828,22 +1827,22 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K9" t="s">
         <v>10</v>
@@ -1870,16 +1869,16 @@
         <v>17</v>
       </c>
       <c r="S9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W9" t="s">
         <v>66</v>
-      </c>
-      <c r="W9" t="s">
-        <v>65</v>
       </c>
       <c r="Y9" t="s">
         <v>19</v>
@@ -1905,7 +1904,7 @@
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -1914,25 +1913,25 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
       </c>
       <c r="I10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K10" t="s">
         <v>10</v>
@@ -1959,16 +1958,16 @@
         <v>17</v>
       </c>
       <c r="S10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W10" t="s">
         <v>71</v>
-      </c>
-      <c r="W10" t="s">
-        <v>70</v>
       </c>
       <c r="Y10" t="s">
         <v>19</v>
@@ -1994,7 +1993,7 @@
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -2003,25 +2002,25 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
         <v>32</v>
       </c>
       <c r="I11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" t="s">
         <v>78</v>
-      </c>
-      <c r="J11" t="s">
-        <v>77</v>
       </c>
       <c r="K11" t="s">
         <v>10</v>
@@ -2048,16 +2047,16 @@
         <v>17</v>
       </c>
       <c r="S11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U11" t="s">
+        <v>78</v>
+      </c>
+      <c r="W11" t="s">
         <v>77</v>
-      </c>
-      <c r="W11" t="s">
-        <v>76</v>
       </c>
       <c r="Y11" t="s">
         <v>19</v>
@@ -2083,7 +2082,7 @@
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
@@ -2092,7 +2091,7 @@
         <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
         <v>29</v>
@@ -2134,16 +2133,16 @@
         <v>17</v>
       </c>
       <c r="S12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U12" t="s">
         <v>7</v>
       </c>
       <c r="W12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y12" t="s">
         <v>19</v>
@@ -2166,7 +2165,7 @@
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
@@ -2175,25 +2174,25 @@
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
         <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s">
         <v>32</v>
       </c>
       <c r="I13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s">
         <v>85</v>
-      </c>
-      <c r="J13" t="s">
-        <v>84</v>
       </c>
       <c r="K13" t="s">
         <v>10</v>
@@ -2220,16 +2219,16 @@
         <v>17</v>
       </c>
       <c r="S13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="T13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Y13" t="s">
         <v>19</v>
@@ -2255,7 +2254,7 @@
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
         <v>26</v>
@@ -2264,25 +2263,25 @@
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
         <v>32</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s">
         <v>10</v>
@@ -2309,16 +2308,16 @@
         <v>17</v>
       </c>
       <c r="S14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y14" t="s">
         <v>19</v>
@@ -2344,7 +2343,7 @@
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
@@ -2353,25 +2352,25 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
         <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K15" t="s">
         <v>10</v>
@@ -2398,19 +2397,19 @@
         <v>17</v>
       </c>
       <c r="S15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V15" t="s">
+        <v>93</v>
+      </c>
+      <c r="W15" t="s">
         <v>92</v>
-      </c>
-      <c r="W15" t="s">
-        <v>91</v>
       </c>
       <c r="Y15" t="s">
         <v>19</v>
@@ -2436,7 +2435,7 @@
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
         <v>26</v>
@@ -2445,22 +2444,22 @@
         <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H16" t="s">
         <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K16" t="s">
         <v>10</v>
@@ -2487,19 +2486,19 @@
         <v>17</v>
       </c>
       <c r="S16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="T16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U16" t="s">
+        <v>96</v>
+      </c>
+      <c r="V16" t="s">
         <v>93</v>
       </c>
-      <c r="U16" t="s">
+      <c r="W16" t="s">
         <v>95</v>
-      </c>
-      <c r="V16" t="s">
-        <v>92</v>
-      </c>
-      <c r="W16" t="s">
-        <v>94</v>
       </c>
       <c r="Y16" t="s">
         <v>19</v>
@@ -2525,7 +2524,7 @@
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
@@ -2534,25 +2533,25 @@
         <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
         <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
         <v>32</v>
       </c>
       <c r="I17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K17" t="s">
         <v>10</v>
@@ -2579,16 +2578,16 @@
         <v>17</v>
       </c>
       <c r="S17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U17" t="s">
+        <v>99</v>
+      </c>
+      <c r="W17" t="s">
         <v>98</v>
-      </c>
-      <c r="W17" t="s">
-        <v>97</v>
       </c>
       <c r="Y17" t="s">
         <v>19</v>
@@ -2614,7 +2613,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
@@ -2623,25 +2622,25 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
         <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H18" t="s">
         <v>32</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K18" t="s">
         <v>10</v>
@@ -2668,16 +2667,16 @@
         <v>17</v>
       </c>
       <c r="S18" t="s">
+        <v>103</v>
+      </c>
+      <c r="T18" t="s">
+        <v>101</v>
+      </c>
+      <c r="U18" t="s">
+        <v>99</v>
+      </c>
+      <c r="W18" t="s">
         <v>102</v>
-      </c>
-      <c r="T18" t="s">
-        <v>100</v>
-      </c>
-      <c r="U18" t="s">
-        <v>98</v>
-      </c>
-      <c r="W18" t="s">
-        <v>101</v>
       </c>
       <c r="Y18" t="s">
         <v>19</v>
@@ -2703,7 +2702,7 @@
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
@@ -2712,25 +2711,25 @@
         <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
         <v>29</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H19" t="s">
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K19" t="s">
         <v>10</v>
@@ -2757,16 +2756,16 @@
         <v>17</v>
       </c>
       <c r="S19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y19" t="s">
         <v>19</v>
@@ -2792,7 +2791,7 @@
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
         <v>26</v>
@@ -2801,25 +2800,25 @@
         <v>27</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
         <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K20" t="s">
         <v>10</v>
@@ -2846,16 +2845,16 @@
         <v>17</v>
       </c>
       <c r="S20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y20" t="s">
         <v>19</v>
@@ -2881,7 +2880,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
@@ -2890,25 +2889,25 @@
         <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
         <v>32</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K21" t="s">
         <v>10</v>
@@ -2935,16 +2934,16 @@
         <v>17</v>
       </c>
       <c r="S21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y21" t="s">
         <v>19</v>
@@ -2970,7 +2969,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
@@ -2979,25 +2978,25 @@
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
         <v>32</v>
       </c>
       <c r="I22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K22" t="s">
         <v>10</v>
@@ -3024,16 +3023,16 @@
         <v>17</v>
       </c>
       <c r="S22" t="s">
+        <v>116</v>
+      </c>
+      <c r="T22" t="s">
+        <v>117</v>
+      </c>
+      <c r="U22" t="s">
+        <v>67</v>
+      </c>
+      <c r="W22" t="s">
         <v>115</v>
-      </c>
-      <c r="T22" t="s">
-        <v>116</v>
-      </c>
-      <c r="U22" t="s">
-        <v>66</v>
-      </c>
-      <c r="W22" t="s">
-        <v>114</v>
       </c>
       <c r="Y22" t="s">
         <v>19</v>
@@ -3059,7 +3058,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
@@ -3068,25 +3067,25 @@
         <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H23" t="s">
         <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K23" t="s">
         <v>10</v>
@@ -3113,16 +3112,16 @@
         <v>17</v>
       </c>
       <c r="S23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y23" t="s">
         <v>19</v>
@@ -3148,7 +3147,7 @@
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
@@ -3157,25 +3156,25 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
         <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>
       </c>
       <c r="I24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K24" t="s">
         <v>10</v>
@@ -3202,16 +3201,16 @@
         <v>17</v>
       </c>
       <c r="S24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="U24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Y24" t="s">
         <v>19</v>
@@ -3237,7 +3236,7 @@
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
@@ -3246,25 +3245,25 @@
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H25" t="s">
         <v>32</v>
       </c>
       <c r="I25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K25" t="s">
         <v>10</v>
@@ -3291,16 +3290,16 @@
         <v>17</v>
       </c>
       <c r="S25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T25" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="U25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W25" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Y25" t="s">
         <v>19</v>
@@ -3326,7 +3325,7 @@
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
@@ -3335,25 +3334,25 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H26" t="s">
         <v>32</v>
       </c>
       <c r="I26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K26" t="s">
         <v>10</v>
@@ -3380,16 +3379,16 @@
         <v>17</v>
       </c>
       <c r="S26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="T26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y26" t="s">
         <v>19</v>
@@ -3415,7 +3414,7 @@
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B27" t="s">
         <v>26</v>
@@ -3424,25 +3423,25 @@
         <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E27" t="s">
         <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H27" t="s">
         <v>32</v>
       </c>
       <c r="I27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K27" t="s">
         <v>10</v>
@@ -3469,16 +3468,16 @@
         <v>17</v>
       </c>
       <c r="S27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="T27" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U27" t="s">
+        <v>131</v>
+      </c>
+      <c r="W27" t="s">
         <v>130</v>
-      </c>
-      <c r="W27" t="s">
-        <v>129</v>
       </c>
       <c r="Y27" t="s">
         <v>19</v>
@@ -3504,7 +3503,7 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B28" t="s">
         <v>26</v>
@@ -3513,25 +3512,25 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E28" t="s">
         <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H28" t="s">
         <v>32</v>
       </c>
       <c r="I28" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" t="s">
         <v>137</v>
-      </c>
-      <c r="J28" t="s">
-        <v>136</v>
       </c>
       <c r="K28" t="s">
         <v>10</v>
@@ -3558,16 +3557,16 @@
         <v>17</v>
       </c>
       <c r="S28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="U28" t="s">
+        <v>137</v>
+      </c>
+      <c r="W28" t="s">
         <v>136</v>
-      </c>
-      <c r="W28" t="s">
-        <v>135</v>
       </c>
       <c r="Y28" t="s">
         <v>19</v>
@@ -3593,7 +3592,7 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B29" t="s">
         <v>26</v>
@@ -3602,7 +3601,7 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E29" t="s">
         <v>29</v>
@@ -3611,16 +3610,16 @@
         <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H29" t="s">
         <v>32</v>
       </c>
       <c r="I29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K29" t="s">
         <v>10</v>
@@ -3650,13 +3649,13 @@
         <v>36</v>
       </c>
       <c r="T29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="U29" t="s">
+        <v>142</v>
+      </c>
+      <c r="W29" t="s">
         <v>141</v>
-      </c>
-      <c r="W29" t="s">
-        <v>140</v>
       </c>
       <c r="Y29" t="s">
         <v>19</v>
@@ -3682,7 +3681,7 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
         <v>26</v>
@@ -3691,7 +3690,7 @@
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -3700,16 +3699,16 @@
         <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H30" t="s">
         <v>32</v>
       </c>
       <c r="I30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K30" t="s">
         <v>10</v>
@@ -3736,16 +3735,16 @@
         <v>17</v>
       </c>
       <c r="S30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="T30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="U30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Y30" t="s">
         <v>19</v>
@@ -3771,34 +3770,34 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K31" t="s">
         <v>10</v>
@@ -3807,16 +3806,16 @@
         <v>11</v>
       </c>
       <c r="M31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O31" t="s">
         <v>14</v>
       </c>
       <c r="P31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q31" t="s">
         <v>16</v>
@@ -3825,22 +3824,22 @@
         <v>17</v>
       </c>
       <c r="S31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="W31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="X31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y31" t="s">
         <v>19</v>
@@ -3855,7 +3854,7 @@
         <v>42</v>
       </c>
       <c r="AC31" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD31" t="s">
         <v>23</v>
@@ -3866,34 +3865,34 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I32" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K32" t="s">
         <v>10</v>
@@ -3902,16 +3901,16 @@
         <v>11</v>
       </c>
       <c r="M32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O32" t="s">
         <v>14</v>
       </c>
       <c r="P32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q32" t="s">
         <v>16</v>
@@ -3920,22 +3919,22 @@
         <v>17</v>
       </c>
       <c r="S32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="T32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="U32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="W32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="X32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y32" t="s">
         <v>19</v>
@@ -3950,7 +3949,7 @@
         <v>42</v>
       </c>
       <c r="AC32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD32" t="s">
         <v>23</v>
@@ -3961,34 +3960,34 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K33" t="s">
         <v>10</v>
@@ -3997,16 +3996,16 @@
         <v>11</v>
       </c>
       <c r="M33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O33" t="s">
         <v>14</v>
       </c>
       <c r="P33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q33" t="s">
         <v>16</v>
@@ -4015,22 +4014,22 @@
         <v>17</v>
       </c>
       <c r="S33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="T33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="X33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y33" t="s">
         <v>19</v>
@@ -4045,7 +4044,7 @@
         <v>42</v>
       </c>
       <c r="AC33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD33" t="s">
         <v>23</v>
@@ -4056,34 +4055,34 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K34" t="s">
         <v>10</v>
@@ -4092,16 +4091,16 @@
         <v>11</v>
       </c>
       <c r="M34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O34" t="s">
         <v>14</v>
       </c>
       <c r="P34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q34" t="s">
         <v>16</v>
@@ -4110,22 +4109,22 @@
         <v>17</v>
       </c>
       <c r="S34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="T34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="U34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="X34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y34" t="s">
         <v>19</v>
@@ -4140,7 +4139,7 @@
         <v>42</v>
       </c>
       <c r="AC34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD34" t="s">
         <v>23</v>
@@ -4151,34 +4150,34 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K35" t="s">
         <v>10</v>
@@ -4187,16 +4186,16 @@
         <v>11</v>
       </c>
       <c r="M35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O35" t="s">
         <v>14</v>
       </c>
       <c r="P35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q35" t="s">
         <v>16</v>
@@ -4205,22 +4204,22 @@
         <v>17</v>
       </c>
       <c r="S35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="T35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W35" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="X35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y35" t="s">
         <v>19</v>
@@ -4235,7 +4234,7 @@
         <v>42</v>
       </c>
       <c r="AC35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD35" t="s">
         <v>23</v>
@@ -4246,34 +4245,34 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K36" t="s">
         <v>10</v>
@@ -4282,16 +4281,16 @@
         <v>11</v>
       </c>
       <c r="M36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O36" t="s">
         <v>14</v>
       </c>
       <c r="P36" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q36" t="s">
         <v>16</v>
@@ -4300,22 +4299,22 @@
         <v>17</v>
       </c>
       <c r="S36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="T36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="V36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="W36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="X36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y36" t="s">
         <v>19</v>
@@ -4330,7 +4329,7 @@
         <v>42</v>
       </c>
       <c r="AC36" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD36" t="s">
         <v>23</v>
@@ -4341,34 +4340,34 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G37" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I37" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K37" t="s">
         <v>10</v>
@@ -4377,16 +4376,16 @@
         <v>11</v>
       </c>
       <c r="M37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O37" t="s">
         <v>14</v>
       </c>
       <c r="P37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q37" t="s">
         <v>16</v>
@@ -4395,22 +4394,22 @@
         <v>17</v>
       </c>
       <c r="S37" t="s">
+        <v>202</v>
+      </c>
+      <c r="T37" t="s">
+        <v>203</v>
+      </c>
+      <c r="U37" t="s">
         <v>201</v>
       </c>
-      <c r="T37" t="s">
-        <v>202</v>
-      </c>
-      <c r="U37" t="s">
+      <c r="V37" t="s">
+        <v>197</v>
+      </c>
+      <c r="W37" t="s">
         <v>200</v>
       </c>
-      <c r="V37" t="s">
-        <v>196</v>
-      </c>
-      <c r="W37" t="s">
-        <v>199</v>
-      </c>
       <c r="X37" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y37" t="s">
         <v>19</v>
@@ -4425,7 +4424,7 @@
         <v>42</v>
       </c>
       <c r="AC37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD37" t="s">
         <v>23</v>
@@ -4436,34 +4435,34 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K38" t="s">
         <v>10</v>
@@ -4472,16 +4471,16 @@
         <v>11</v>
       </c>
       <c r="M38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O38" t="s">
         <v>14</v>
       </c>
       <c r="P38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q38" t="s">
         <v>16</v>
@@ -4490,22 +4489,22 @@
         <v>17</v>
       </c>
       <c r="S38" t="s">
+        <v>202</v>
+      </c>
+      <c r="T38" t="s">
+        <v>206</v>
+      </c>
+      <c r="U38" t="s">
         <v>201</v>
       </c>
-      <c r="T38" t="s">
+      <c r="V38" t="s">
+        <v>177</v>
+      </c>
+      <c r="W38" t="s">
         <v>205</v>
       </c>
-      <c r="U38" t="s">
-        <v>200</v>
-      </c>
-      <c r="V38" t="s">
-        <v>176</v>
-      </c>
-      <c r="W38" t="s">
-        <v>204</v>
-      </c>
       <c r="X38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y38" t="s">
         <v>19</v>
@@ -4520,7 +4519,7 @@
         <v>42</v>
       </c>
       <c r="AC38" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD38" t="s">
         <v>23</v>
@@ -4531,34 +4530,34 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B39" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F39" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K39" t="s">
         <v>10</v>
@@ -4567,16 +4566,16 @@
         <v>11</v>
       </c>
       <c r="M39" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O39" t="s">
         <v>14</v>
       </c>
       <c r="P39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q39" t="s">
         <v>16</v>
@@ -4585,22 +4584,22 @@
         <v>17</v>
       </c>
       <c r="S39" t="s">
+        <v>202</v>
+      </c>
+      <c r="T39" t="s">
+        <v>209</v>
+      </c>
+      <c r="U39" t="s">
         <v>201</v>
       </c>
-      <c r="T39" t="s">
+      <c r="V39" t="s">
+        <v>190</v>
+      </c>
+      <c r="W39" t="s">
         <v>208</v>
       </c>
-      <c r="U39" t="s">
-        <v>200</v>
-      </c>
-      <c r="V39" t="s">
-        <v>189</v>
-      </c>
-      <c r="W39" t="s">
-        <v>207</v>
-      </c>
       <c r="X39" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y39" t="s">
         <v>19</v>
@@ -4615,7 +4614,7 @@
         <v>42</v>
       </c>
       <c r="AC39" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD39" t="s">
         <v>23</v>
@@ -4626,34 +4625,34 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F40" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K40" t="s">
         <v>10</v>
@@ -4662,16 +4661,16 @@
         <v>11</v>
       </c>
       <c r="M40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O40" t="s">
         <v>14</v>
       </c>
       <c r="P40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q40" t="s">
         <v>16</v>
@@ -4680,22 +4679,22 @@
         <v>17</v>
       </c>
       <c r="S40" t="s">
+        <v>202</v>
+      </c>
+      <c r="T40" t="s">
+        <v>212</v>
+      </c>
+      <c r="U40" t="s">
         <v>201</v>
       </c>
-      <c r="T40" t="s">
+      <c r="V40" t="s">
+        <v>171</v>
+      </c>
+      <c r="W40" t="s">
         <v>211</v>
       </c>
-      <c r="U40" t="s">
-        <v>200</v>
-      </c>
-      <c r="V40" t="s">
-        <v>170</v>
-      </c>
-      <c r="W40" t="s">
-        <v>210</v>
-      </c>
       <c r="X40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y40" t="s">
         <v>19</v>
@@ -4710,7 +4709,7 @@
         <v>42</v>
       </c>
       <c r="AC40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD40" t="s">
         <v>23</v>
@@ -4721,34 +4720,34 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D41" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F41" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H41" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K41" t="s">
         <v>10</v>
@@ -4757,16 +4756,16 @@
         <v>11</v>
       </c>
       <c r="M41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O41" t="s">
         <v>14</v>
       </c>
       <c r="P41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q41" t="s">
         <v>16</v>
@@ -4775,22 +4774,22 @@
         <v>17</v>
       </c>
       <c r="S41" t="s">
+        <v>202</v>
+      </c>
+      <c r="T41" t="s">
+        <v>215</v>
+      </c>
+      <c r="U41" t="s">
         <v>201</v>
       </c>
-      <c r="T41" t="s">
+      <c r="V41" t="s">
+        <v>184</v>
+      </c>
+      <c r="W41" t="s">
         <v>214</v>
       </c>
-      <c r="U41" t="s">
-        <v>200</v>
-      </c>
-      <c r="V41" t="s">
-        <v>183</v>
-      </c>
-      <c r="W41" t="s">
-        <v>213</v>
-      </c>
       <c r="X41" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y41" t="s">
         <v>19</v>
@@ -4805,7 +4804,7 @@
         <v>42</v>
       </c>
       <c r="AC41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD41" t="s">
         <v>23</v>
@@ -4816,34 +4815,34 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H42" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K42" t="s">
         <v>10</v>
@@ -4852,16 +4851,16 @@
         <v>11</v>
       </c>
       <c r="M42" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O42" t="s">
         <v>14</v>
       </c>
       <c r="P42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q42" t="s">
         <v>16</v>
@@ -4870,22 +4869,22 @@
         <v>17</v>
       </c>
       <c r="S42" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T42" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="U42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="V42" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="W42" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="X42" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Y42" t="s">
         <v>19</v>
@@ -4900,7 +4899,7 @@
         <v>42</v>
       </c>
       <c r="AC42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD42" t="s">
         <v>23</v>
@@ -4911,34 +4910,34 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G43" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K43" t="s">
         <v>10</v>
@@ -4947,16 +4946,16 @@
         <v>11</v>
       </c>
       <c r="M43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O43" t="s">
         <v>14</v>
       </c>
       <c r="P43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43" t="s">
         <v>16</v>
@@ -4965,22 +4964,22 @@
         <v>17</v>
       </c>
       <c r="S43" t="s">
+        <v>228</v>
+      </c>
+      <c r="T43" t="s">
+        <v>229</v>
+      </c>
+      <c r="U43" t="s">
         <v>227</v>
       </c>
-      <c r="T43" t="s">
-        <v>228</v>
-      </c>
-      <c r="U43" t="s">
+      <c r="V43" t="s">
+        <v>171</v>
+      </c>
+      <c r="W43" t="s">
         <v>226</v>
       </c>
-      <c r="V43" t="s">
-        <v>170</v>
-      </c>
-      <c r="W43" t="s">
-        <v>225</v>
-      </c>
       <c r="X43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y43" t="s">
         <v>19</v>
@@ -4995,7 +4994,7 @@
         <v>42</v>
       </c>
       <c r="AC43" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD43" t="s">
         <v>23</v>
@@ -5006,34 +5005,34 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D44" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G44" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K44" t="s">
         <v>10</v>
@@ -5042,16 +5041,16 @@
         <v>11</v>
       </c>
       <c r="M44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" t="s">
         <v>14</v>
       </c>
       <c r="P44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q44" t="s">
         <v>16</v>
@@ -5060,22 +5059,22 @@
         <v>17</v>
       </c>
       <c r="S44" t="s">
+        <v>228</v>
+      </c>
+      <c r="T44" t="s">
+        <v>232</v>
+      </c>
+      <c r="U44" t="s">
         <v>227</v>
       </c>
-      <c r="T44" t="s">
-        <v>231</v>
-      </c>
-      <c r="U44" t="s">
-        <v>226</v>
-      </c>
       <c r="V44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="W44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="X44" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y44" t="s">
         <v>19</v>
@@ -5090,7 +5089,7 @@
         <v>42</v>
       </c>
       <c r="AC44" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD44" t="s">
         <v>23</v>
@@ -5101,34 +5100,34 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K45" t="s">
         <v>10</v>
@@ -5137,16 +5136,16 @@
         <v>11</v>
       </c>
       <c r="M45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O45" t="s">
         <v>14</v>
       </c>
       <c r="P45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q45" t="s">
         <v>16</v>
@@ -5155,22 +5154,22 @@
         <v>17</v>
       </c>
       <c r="S45" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="T45" t="s">
+        <v>235</v>
+      </c>
+      <c r="U45" t="s">
+        <v>227</v>
+      </c>
+      <c r="V45" t="s">
+        <v>184</v>
+      </c>
+      <c r="W45" t="s">
         <v>234</v>
       </c>
-      <c r="U45" t="s">
-        <v>226</v>
-      </c>
-      <c r="V45" t="s">
-        <v>183</v>
-      </c>
-      <c r="W45" t="s">
-        <v>233</v>
-      </c>
       <c r="X45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y45" t="s">
         <v>19</v>
@@ -5185,7 +5184,7 @@
         <v>42</v>
       </c>
       <c r="AC45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD45" t="s">
         <v>23</v>
@@ -5196,34 +5195,34 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G46" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I46" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K46" t="s">
         <v>10</v>
@@ -5232,16 +5231,16 @@
         <v>11</v>
       </c>
       <c r="M46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O46" t="s">
         <v>14</v>
       </c>
       <c r="P46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q46" t="s">
         <v>16</v>
@@ -5250,22 +5249,22 @@
         <v>17</v>
       </c>
       <c r="S46" t="s">
+        <v>238</v>
+      </c>
+      <c r="T46" t="s">
+        <v>239</v>
+      </c>
+      <c r="U46" t="s">
+        <v>227</v>
+      </c>
+      <c r="V46" t="s">
+        <v>190</v>
+      </c>
+      <c r="W46" t="s">
         <v>237</v>
       </c>
-      <c r="T46" t="s">
-        <v>238</v>
-      </c>
-      <c r="U46" t="s">
-        <v>226</v>
-      </c>
-      <c r="V46" t="s">
-        <v>189</v>
-      </c>
-      <c r="W46" t="s">
-        <v>236</v>
-      </c>
       <c r="X46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y46" t="s">
         <v>19</v>
@@ -5280,7 +5279,7 @@
         <v>42</v>
       </c>
       <c r="AC46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD46" t="s">
         <v>23</v>
@@ -5291,34 +5290,34 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D47" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K47" t="s">
         <v>10</v>
@@ -5327,16 +5326,16 @@
         <v>11</v>
       </c>
       <c r="M47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O47" t="s">
         <v>14</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q47" t="s">
         <v>16</v>
@@ -5345,22 +5344,22 @@
         <v>17</v>
       </c>
       <c r="S47" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T47" t="s">
+        <v>242</v>
+      </c>
+      <c r="U47" t="s">
+        <v>227</v>
+      </c>
+      <c r="V47" t="s">
+        <v>197</v>
+      </c>
+      <c r="W47" t="s">
         <v>241</v>
       </c>
-      <c r="U47" t="s">
-        <v>226</v>
-      </c>
-      <c r="V47" t="s">
-        <v>196</v>
-      </c>
-      <c r="W47" t="s">
-        <v>240</v>
-      </c>
       <c r="X47" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y47" t="s">
         <v>19</v>
@@ -5375,7 +5374,7 @@
         <v>42</v>
       </c>
       <c r="AC47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD47" t="s">
         <v>23</v>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26646D90-CB2F-4DB4-9815-E46B873BD90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E55FE1-5C16-44A0-97FD-6774B99E1780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$47</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1091,6 +1094,9 @@
   <dimension ref="A1:AF47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="23.19921875" customWidth="1"/>
+    <col min="2" max="2" width="16.19921875" customWidth="1"/>
+    <col min="9" max="9" width="18.19921875" customWidth="1"/>
     <col min="21" max="21" width="12.33203125" customWidth="1"/>
     <col min="22" max="22" width="20.06640625" customWidth="1"/>
   </cols>
@@ -5384,6 +5390,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AF47" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -8,22 +8,112 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E55FE1-5C16-44A0-97FD-6774B99E1780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C2220F-38B2-466A-8029-9656200EA75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$47</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="277">
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
   <si>
     <t>Update Terakhir</t>
   </si>
@@ -97,7 +187,7 @@
     <t>--- (Tidak Ada / Kosong) ---</t>
   </si>
   <si>
-    <t>2026-09-14 12:26:04</t>
+    <t>2026-09-14 18:26:29</t>
   </si>
   <si>
     <t>005/BSS-JOB/WS/V/2026</t>
@@ -283,9 +373,6 @@
     <t>30 Jan 2026</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>013/BSS-JOB/WS/VIII/2026</t>
   </si>
   <si>
@@ -752,6 +839,18 @@
   </si>
   <si>
     <t>7207250142-BSS-WCC-2026-006C</t>
+  </si>
+  <si>
+    <t>001/BSS-JOB/WH/X/2025</t>
+  </si>
+  <si>
+    <t>31 Oct 2025</t>
+  </si>
+  <si>
+    <t>4500010394</t>
+  </si>
+  <si>
+    <t>01 Oct 2025</t>
   </si>
 </sst>
 </file>
@@ -1091,4306 +1190,4399 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF47"/>
+  <dimension ref="A1:AF48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.19921875" customWidth="1"/>
-    <col min="2" max="2" width="16.19921875" customWidth="1"/>
-    <col min="9" max="9" width="18.19921875" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" customWidth="1"/>
-    <col min="22" max="22" width="20.06640625" customWidth="1"/>
+    <col min="1" max="1" width="26.1328125" customWidth="1"/>
+    <col min="2" max="2" width="18.06640625" customWidth="1"/>
+    <col min="8" max="8" width="11.796875" customWidth="1"/>
+    <col min="9" max="9" width="17.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="A1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
       <c r="AF1" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="O2" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q2" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="T2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="U2" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="V2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="W2" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="X2" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z2" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB2" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="AC2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="AD2" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P3" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q3" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R3" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S3" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="T3" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="U3" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="W3" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="Y3" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z3" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA3" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB3" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC3" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD3" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF3" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M4" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N4" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O4" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P4" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q4" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R4" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S4" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="U4" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="W4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB4" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AD4" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF4" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J5" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+      <c r="O5" t="s">
         <v>45</v>
       </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="P5" t="s">
         <v>46</v>
       </c>
-      <c r="J5" t="s">
+      <c r="Q5" t="s">
         <v>47</v>
       </c>
-      <c r="K5" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" t="s">
-        <v>14</v>
-      </c>
-      <c r="P5" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>16</v>
-      </c>
       <c r="R5" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S5" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="U5" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="V5" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="X5" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="Y5" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z5" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA5" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB5" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC5" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD5" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF5" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" t="s">
+        <v>84</v>
+      </c>
+      <c r="T6" t="s">
+        <v>80</v>
+      </c>
+      <c r="U6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V6" t="s">
+        <v>80</v>
+      </c>
+      <c r="W6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y6" t="s">
         <v>50</v>
       </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="Z6" t="s">
         <v>51</v>
       </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="AA6" t="s">
         <v>52</v>
       </c>
-      <c r="K6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M6" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O6" t="s">
-        <v>14</v>
-      </c>
-      <c r="P6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>16</v>
-      </c>
-      <c r="R6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S6" t="s">
-        <v>53</v>
-      </c>
-      <c r="T6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U6" t="s">
-        <v>51</v>
-      </c>
-      <c r="V6" t="s">
-        <v>49</v>
-      </c>
-      <c r="W6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>21</v>
-      </c>
       <c r="AB6" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC6" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF6" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" t="s">
+        <v>48</v>
+      </c>
+      <c r="S7" t="s">
+        <v>90</v>
+      </c>
+      <c r="T7" t="s">
+        <v>85</v>
+      </c>
+      <c r="U7" t="s">
+        <v>88</v>
+      </c>
+      <c r="W7" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="AF7" t="s">
         <v>55</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" t="s">
-        <v>10</v>
-      </c>
-      <c r="L7" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>16</v>
-      </c>
-      <c r="R7" t="s">
-        <v>17</v>
-      </c>
-      <c r="S7" t="s">
-        <v>59</v>
-      </c>
-      <c r="T7" t="s">
-        <v>54</v>
-      </c>
-      <c r="U7" t="s">
-        <v>57</v>
-      </c>
-      <c r="W7" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
-      </c>
       <c r="G8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" t="s">
         <v>63</v>
       </c>
-      <c r="H8" t="s">
-        <v>32</v>
-      </c>
       <c r="J8" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O8" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P8" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q8" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R8" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S8" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="T8" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="U8" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="W8" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="Y8" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z8" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA8" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB8" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD8" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF8" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" t="s">
         <v>65</v>
       </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="N9" t="s">
         <v>66</v>
       </c>
-      <c r="E9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" t="s">
-        <v>68</v>
-      </c>
-      <c r="K9" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M9" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9" t="s">
-        <v>35</v>
-      </c>
       <c r="O9" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P9" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R9" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S9" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="T9" t="s">
+        <v>96</v>
+      </c>
+      <c r="U9" t="s">
+        <v>98</v>
+      </c>
+      <c r="W9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB9" t="s">
         <v>65</v>
       </c>
-      <c r="U9" t="s">
-        <v>67</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="AC9" t="s">
         <v>66</v>
       </c>
-      <c r="Y9" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>35</v>
-      </c>
       <c r="AD9" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF9" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L10" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N10" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O10" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P10" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R10" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S10" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="T10" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="U10" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="W10" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="Y10" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z10" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA10" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB10" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC10" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD10" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF10" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L11" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N11" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O11" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P11" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R11" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S11" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="T11" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="U11" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="W11" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z11" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA11" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB11" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC11" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD11" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF11" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="K12" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L12" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N12" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O12" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P12" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q12" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R12" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S12" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="T12" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="U12" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="W12" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="Y12" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z12" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA12" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB12" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AD12" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF12" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="K13" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L13" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N13" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O13" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P13" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R13" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S13" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="T13" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="U13" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="W13" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z13" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA13" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB13" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC13" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD13" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF13" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
         <v>87</v>
       </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="K14" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L14" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N14" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O14" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P14" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q14" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R14" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S14" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="T14" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="U14" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="W14" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="Y14" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z14" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA14" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB14" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC14" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD14" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF14" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="J15" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="K15" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L15" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N15" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O15" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P15" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q15" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R15" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S15" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="T15" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="U15" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="V15" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="W15" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="Y15" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z15" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA15" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB15" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC15" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD15" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF15" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="J16" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="K16" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L16" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N16" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O16" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P16" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q16" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R16" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S16" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="T16" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="U16" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="V16" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="W16" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="Y16" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z16" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA16" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB16" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC16" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD16" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF16" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="K17" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L17" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M17" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N17" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O17" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P17" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q17" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R17" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S17" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="T17" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="U17" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="W17" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="Y17" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z17" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA17" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB17" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC17" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD17" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF17" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="H18" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="K18" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L18" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N18" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O18" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P18" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q18" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R18" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S18" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="T18" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="U18" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="W18" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="Y18" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z18" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA18" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB18" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC18" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD18" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF18" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="H19" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="K19" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L19" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M19" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N19" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O19" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P19" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q19" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R19" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S19" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="T19" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="U19" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="W19" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="Y19" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z19" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA19" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB19" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC19" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD19" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF19" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H20" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="K20" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L20" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M20" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N20" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O20" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P20" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q20" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R20" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S20" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="T20" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="U20" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="W20" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="Y20" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z20" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA20" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB20" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC20" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD20" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF20" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="K21" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L21" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M21" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N21" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O21" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P21" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q21" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R21" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S21" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="T21" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="U21" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="W21" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="Y21" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z21" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA21" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB21" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC21" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD21" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF21" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="K22" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L22" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M22" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N22" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O22" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P22" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q22" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R22" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S22" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="T22" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="U22" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="W22" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="Y22" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z22" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA22" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB22" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC22" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD22" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF22" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K23" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L23" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M23" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N23" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O23" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P23" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q23" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R23" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S23" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="T23" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="U23" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="W23" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="Y23" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z23" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA23" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB23" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC23" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD23" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF23" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="K24" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L24" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N24" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O24" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P24" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q24" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R24" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S24" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="T24" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="U24" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="W24" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="Y24" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA24" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB24" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC24" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD24" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF24" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="K25" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L25" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M25" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N25" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O25" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P25" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q25" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R25" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S25" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="T25" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="U25" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="W25" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="Y25" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z25" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA25" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB25" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC25" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD25" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF25" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D26" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="E26" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="K26" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L26" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N26" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O26" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P26" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q26" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R26" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S26" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="T26" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="U26" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="W26" t="s">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="Y26" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z26" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA26" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB26" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC26" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD26" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF26" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="E27" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="H27" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="J27" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="K27" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L27" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M27" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N27" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O27" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P27" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q27" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R27" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S27" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="T27" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="U27" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="W27" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="Y27" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z27" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA27" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB27" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC27" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD27" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF27" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="H28" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="J28" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="K28" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L28" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M28" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N28" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O28" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P28" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R28" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S28" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="T28" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="U28" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="W28" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="Y28" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z28" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA28" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB28" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC28" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD28" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF28" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="E29" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G29" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="H29" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="J29" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="K29" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L29" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M29" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N29" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O29" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P29" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q29" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R29" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S29" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="T29" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="U29" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="W29" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="Y29" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z29" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA29" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB29" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC29" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD29" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF29" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="E30" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="G30" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="H30" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="J30" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="K30" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L30" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M30" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="N30" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="O30" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P30" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q30" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R30" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S30" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="T30" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="U30" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="W30" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="Y30" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z30" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA30" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB30" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AC30" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AD30" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF30" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G31" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="H31" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I31" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="J31" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K31" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L31" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M31" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N31" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O31" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P31" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q31" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R31" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S31" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="T31" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="U31" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="V31" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="W31" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="X31" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="Y31" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z31" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA31" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB31" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC31" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD31" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF31" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D32" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G32" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="H32" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I32" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="J32" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K32" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L32" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M32" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N32" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O32" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P32" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q32" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R32" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S32" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="T32" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="U32" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="V32" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="W32" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="X32" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="Y32" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z32" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA32" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB32" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC32" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD32" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF32" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F33" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G33" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="H33" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I33" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J33" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K33" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L33" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M33" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N33" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O33" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P33" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q33" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R33" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S33" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="T33" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="U33" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="V33" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="W33" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="X33" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="Y33" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z33" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA33" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB33" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC33" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD33" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF33" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" t="s">
         <v>180</v>
       </c>
-      <c r="B34" t="s">
-        <v>150</v>
-      </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D34" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="E34" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F34" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G34" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="H34" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I34" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="J34" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K34" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L34" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M34" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N34" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O34" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P34" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q34" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R34" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S34" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="T34" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="U34" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="V34" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="W34" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="X34" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="Y34" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z34" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA34" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB34" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC34" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD34" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF34" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
+        <v>217</v>
+      </c>
+      <c r="E35" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" t="s">
+        <v>185</v>
+      </c>
+      <c r="I35" t="s">
+        <v>218</v>
+      </c>
+      <c r="J35" t="s">
         <v>187</v>
       </c>
-      <c r="E35" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" t="s">
-        <v>153</v>
-      </c>
-      <c r="G35" t="s">
-        <v>154</v>
-      </c>
-      <c r="H35" t="s">
-        <v>155</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="K35" t="s">
+        <v>41</v>
+      </c>
+      <c r="L35" t="s">
+        <v>42</v>
+      </c>
+      <c r="M35" t="s">
         <v>188</v>
       </c>
-      <c r="J35" t="s">
-        <v>157</v>
-      </c>
-      <c r="K35" t="s">
-        <v>10</v>
-      </c>
-      <c r="L35" t="s">
-        <v>11</v>
-      </c>
-      <c r="M35" t="s">
-        <v>158</v>
-      </c>
       <c r="N35" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O35" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P35" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q35" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R35" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S35" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="T35" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="U35" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="V35" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="W35" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="X35" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="Y35" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z35" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA35" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB35" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC35" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD35" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF35" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C36" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F36" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G36" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="H36" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I36" t="s">
+        <v>225</v>
+      </c>
+      <c r="J36" t="s">
+        <v>187</v>
+      </c>
+      <c r="K36" t="s">
+        <v>41</v>
+      </c>
+      <c r="L36" t="s">
+        <v>42</v>
+      </c>
+      <c r="M36" t="s">
+        <v>188</v>
+      </c>
+      <c r="N36" t="s">
+        <v>189</v>
+      </c>
+      <c r="O36" t="s">
+        <v>45</v>
+      </c>
+      <c r="P36" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>47</v>
+      </c>
+      <c r="R36" t="s">
+        <v>48</v>
+      </c>
+      <c r="S36" t="s">
+        <v>199</v>
+      </c>
+      <c r="T36" t="s">
+        <v>226</v>
+      </c>
+      <c r="U36" t="s">
+        <v>184</v>
+      </c>
+      <c r="V36" t="s">
+        <v>227</v>
+      </c>
+      <c r="W36" t="s">
+        <v>224</v>
+      </c>
+      <c r="X36" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s">
         <v>195</v>
       </c>
-      <c r="J36" t="s">
-        <v>157</v>
-      </c>
-      <c r="K36" t="s">
-        <v>10</v>
-      </c>
-      <c r="L36" t="s">
-        <v>11</v>
-      </c>
-      <c r="M36" t="s">
-        <v>158</v>
-      </c>
-      <c r="N36" t="s">
-        <v>159</v>
-      </c>
-      <c r="O36" t="s">
-        <v>14</v>
-      </c>
-      <c r="P36" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>16</v>
-      </c>
-      <c r="R36" t="s">
-        <v>17</v>
-      </c>
-      <c r="S36" t="s">
-        <v>169</v>
-      </c>
-      <c r="T36" t="s">
-        <v>196</v>
-      </c>
-      <c r="U36" t="s">
-        <v>154</v>
-      </c>
-      <c r="V36" t="s">
-        <v>197</v>
-      </c>
-      <c r="W36" t="s">
-        <v>194</v>
-      </c>
-      <c r="X36" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z36" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>165</v>
-      </c>
       <c r="AD36" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF36" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G37" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="H37" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I37" t="s">
+        <v>225</v>
+      </c>
+      <c r="J37" t="s">
+        <v>187</v>
+      </c>
+      <c r="K37" t="s">
+        <v>41</v>
+      </c>
+      <c r="L37" t="s">
+        <v>42</v>
+      </c>
+      <c r="M37" t="s">
+        <v>188</v>
+      </c>
+      <c r="N37" t="s">
+        <v>189</v>
+      </c>
+      <c r="O37" t="s">
+        <v>45</v>
+      </c>
+      <c r="P37" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>47</v>
+      </c>
+      <c r="R37" t="s">
+        <v>48</v>
+      </c>
+      <c r="S37" t="s">
+        <v>232</v>
+      </c>
+      <c r="T37" t="s">
+        <v>233</v>
+      </c>
+      <c r="U37" t="s">
+        <v>231</v>
+      </c>
+      <c r="V37" t="s">
+        <v>227</v>
+      </c>
+      <c r="W37" t="s">
+        <v>230</v>
+      </c>
+      <c r="X37" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s">
         <v>195</v>
       </c>
-      <c r="J37" t="s">
-        <v>157</v>
-      </c>
-      <c r="K37" t="s">
-        <v>10</v>
-      </c>
-      <c r="L37" t="s">
-        <v>11</v>
-      </c>
-      <c r="M37" t="s">
-        <v>158</v>
-      </c>
-      <c r="N37" t="s">
-        <v>159</v>
-      </c>
-      <c r="O37" t="s">
-        <v>14</v>
-      </c>
-      <c r="P37" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>16</v>
-      </c>
-      <c r="R37" t="s">
-        <v>17</v>
-      </c>
-      <c r="S37" t="s">
-        <v>202</v>
-      </c>
-      <c r="T37" t="s">
-        <v>203</v>
-      </c>
-      <c r="U37" t="s">
-        <v>201</v>
-      </c>
-      <c r="V37" t="s">
-        <v>197</v>
-      </c>
-      <c r="W37" t="s">
-        <v>200</v>
-      </c>
-      <c r="X37" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z37" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB37" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>165</v>
-      </c>
       <c r="AD37" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF37" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
+        <v>235</v>
+      </c>
+      <c r="E38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" t="s">
+        <v>183</v>
+      </c>
+      <c r="G38" t="s">
+        <v>231</v>
+      </c>
+      <c r="H38" t="s">
+        <v>185</v>
+      </c>
+      <c r="I38" t="s">
         <v>205</v>
       </c>
-      <c r="E38" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" t="s">
-        <v>153</v>
-      </c>
-      <c r="G38" t="s">
-        <v>201</v>
-      </c>
-      <c r="H38" t="s">
-        <v>155</v>
-      </c>
-      <c r="I38" t="s">
-        <v>175</v>
-      </c>
       <c r="J38" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K38" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L38" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M38" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N38" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O38" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P38" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q38" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R38" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S38" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="T38" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="U38" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="V38" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="W38" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="X38" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="Y38" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z38" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA38" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB38" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC38" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD38" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF38" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D39" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G39" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="H39" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I39" t="s">
+        <v>218</v>
+      </c>
+      <c r="J39" t="s">
+        <v>187</v>
+      </c>
+      <c r="K39" t="s">
+        <v>41</v>
+      </c>
+      <c r="L39" t="s">
+        <v>42</v>
+      </c>
+      <c r="M39" t="s">
         <v>188</v>
       </c>
-      <c r="J39" t="s">
-        <v>157</v>
-      </c>
-      <c r="K39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L39" t="s">
-        <v>11</v>
-      </c>
-      <c r="M39" t="s">
-        <v>158</v>
-      </c>
       <c r="N39" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O39" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P39" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q39" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R39" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S39" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="T39" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="U39" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="V39" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="W39" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="X39" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="Y39" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z39" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA39" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB39" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC39" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD39" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF39" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C40" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D40" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F40" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G40" t="s">
+        <v>231</v>
+      </c>
+      <c r="H40" t="s">
+        <v>185</v>
+      </c>
+      <c r="I40" t="s">
+        <v>198</v>
+      </c>
+      <c r="J40" t="s">
+        <v>187</v>
+      </c>
+      <c r="K40" t="s">
+        <v>41</v>
+      </c>
+      <c r="L40" t="s">
+        <v>42</v>
+      </c>
+      <c r="M40" t="s">
+        <v>188</v>
+      </c>
+      <c r="N40" t="s">
+        <v>189</v>
+      </c>
+      <c r="O40" t="s">
+        <v>45</v>
+      </c>
+      <c r="P40" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>47</v>
+      </c>
+      <c r="R40" t="s">
+        <v>48</v>
+      </c>
+      <c r="S40" t="s">
+        <v>232</v>
+      </c>
+      <c r="T40" t="s">
+        <v>242</v>
+      </c>
+      <c r="U40" t="s">
+        <v>231</v>
+      </c>
+      <c r="V40" t="s">
         <v>201</v>
       </c>
-      <c r="H40" t="s">
-        <v>155</v>
-      </c>
-      <c r="I40" t="s">
-        <v>168</v>
-      </c>
-      <c r="J40" t="s">
-        <v>157</v>
-      </c>
-      <c r="K40" t="s">
-        <v>10</v>
-      </c>
-      <c r="L40" t="s">
-        <v>11</v>
-      </c>
-      <c r="M40" t="s">
-        <v>158</v>
-      </c>
-      <c r="N40" t="s">
-        <v>159</v>
-      </c>
-      <c r="O40" t="s">
-        <v>14</v>
-      </c>
-      <c r="P40" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>16</v>
-      </c>
-      <c r="R40" t="s">
-        <v>17</v>
-      </c>
-      <c r="S40" t="s">
+      <c r="W40" t="s">
+        <v>241</v>
+      </c>
+      <c r="X40" t="s">
         <v>202</v>
       </c>
-      <c r="T40" t="s">
-        <v>212</v>
-      </c>
-      <c r="U40" t="s">
-        <v>201</v>
-      </c>
-      <c r="V40" t="s">
-        <v>171</v>
-      </c>
-      <c r="W40" t="s">
-        <v>211</v>
-      </c>
-      <c r="X40" t="s">
-        <v>172</v>
-      </c>
       <c r="Y40" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z40" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA40" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB40" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC40" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD40" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF40" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
+        <v>244</v>
+      </c>
+      <c r="E41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F41" t="s">
+        <v>183</v>
+      </c>
+      <c r="G41" t="s">
+        <v>231</v>
+      </c>
+      <c r="H41" t="s">
+        <v>185</v>
+      </c>
+      <c r="I41" t="s">
+        <v>212</v>
+      </c>
+      <c r="J41" t="s">
+        <v>187</v>
+      </c>
+      <c r="K41" t="s">
+        <v>41</v>
+      </c>
+      <c r="L41" t="s">
+        <v>42</v>
+      </c>
+      <c r="M41" t="s">
+        <v>188</v>
+      </c>
+      <c r="N41" t="s">
+        <v>189</v>
+      </c>
+      <c r="O41" t="s">
+        <v>45</v>
+      </c>
+      <c r="P41" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>47</v>
+      </c>
+      <c r="R41" t="s">
+        <v>48</v>
+      </c>
+      <c r="S41" t="s">
+        <v>232</v>
+      </c>
+      <c r="T41" t="s">
+        <v>245</v>
+      </c>
+      <c r="U41" t="s">
+        <v>231</v>
+      </c>
+      <c r="V41" t="s">
         <v>214</v>
       </c>
-      <c r="E41" t="s">
-        <v>62</v>
-      </c>
-      <c r="F41" t="s">
-        <v>153</v>
-      </c>
-      <c r="G41" t="s">
-        <v>201</v>
-      </c>
-      <c r="H41" t="s">
-        <v>155</v>
-      </c>
-      <c r="I41" t="s">
-        <v>182</v>
-      </c>
-      <c r="J41" t="s">
-        <v>157</v>
-      </c>
-      <c r="K41" t="s">
-        <v>10</v>
-      </c>
-      <c r="L41" t="s">
-        <v>11</v>
-      </c>
-      <c r="M41" t="s">
-        <v>158</v>
-      </c>
-      <c r="N41" t="s">
-        <v>159</v>
-      </c>
-      <c r="O41" t="s">
-        <v>14</v>
-      </c>
-      <c r="P41" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>16</v>
-      </c>
-      <c r="R41" t="s">
-        <v>17</v>
-      </c>
-      <c r="S41" t="s">
-        <v>202</v>
-      </c>
-      <c r="T41" t="s">
+      <c r="W41" t="s">
+        <v>244</v>
+      </c>
+      <c r="X41" t="s">
         <v>215</v>
       </c>
-      <c r="U41" t="s">
-        <v>201</v>
-      </c>
-      <c r="V41" t="s">
-        <v>184</v>
-      </c>
-      <c r="W41" t="s">
-        <v>214</v>
-      </c>
-      <c r="X41" t="s">
-        <v>185</v>
-      </c>
       <c r="Y41" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z41" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA41" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB41" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC41" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD41" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF41" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D42" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="E42" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F42" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G42" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="H42" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I42" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="J42" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="K42" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L42" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M42" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N42" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O42" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P42" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q42" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R42" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S42" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="T42" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="U42" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="V42" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="W42" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="X42" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="Y42" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z42" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA42" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB42" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC42" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD42" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF42" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D43" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F43" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G43" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="H43" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I43" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="J43" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K43" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L43" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M43" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N43" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O43" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P43" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q43" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R43" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S43" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="T43" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="U43" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="V43" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="W43" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="X43" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="Y43" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z43" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA43" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB43" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC43" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD43" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF43" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C44" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D44" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F44" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G44" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="H44" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I44" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="J44" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K44" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L44" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M44" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N44" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O44" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P44" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q44" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R44" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S44" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="T44" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="U44" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="V44" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="W44" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="X44" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="Y44" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z44" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA44" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB44" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC44" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD44" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF44" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D45" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F45" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G45" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="H45" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I45" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="J45" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="K45" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="L45" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M45" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N45" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O45" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P45" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q45" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R45" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S45" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="T45" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="U45" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="V45" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="W45" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="X45" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="Y45" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z45" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA45" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB45" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC45" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD45" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF45" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="B46" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C46" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D46" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F46" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G46" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="H46" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I46" t="s">
+        <v>218</v>
+      </c>
+      <c r="J46" t="s">
+        <v>187</v>
+      </c>
+      <c r="K46" t="s">
+        <v>41</v>
+      </c>
+      <c r="L46" t="s">
+        <v>42</v>
+      </c>
+      <c r="M46" t="s">
         <v>188</v>
       </c>
-      <c r="J46" t="s">
-        <v>157</v>
-      </c>
-      <c r="K46" t="s">
-        <v>10</v>
-      </c>
-      <c r="L46" t="s">
-        <v>11</v>
-      </c>
-      <c r="M46" t="s">
-        <v>158</v>
-      </c>
       <c r="N46" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="O46" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="P46" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Q46" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="R46" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S46" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="T46" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="U46" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="V46" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="W46" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="X46" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="Y46" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="Z46" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="AA46" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="AB46" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="AC46" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AD46" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="AF46" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="E47" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="F47" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="G47" t="s">
+        <v>257</v>
+      </c>
+      <c r="H47" t="s">
+        <v>185</v>
+      </c>
+      <c r="I47" t="s">
+        <v>225</v>
+      </c>
+      <c r="J47" t="s">
+        <v>187</v>
+      </c>
+      <c r="K47" t="s">
+        <v>41</v>
+      </c>
+      <c r="L47" t="s">
+        <v>42</v>
+      </c>
+      <c r="M47" t="s">
+        <v>188</v>
+      </c>
+      <c r="N47" t="s">
+        <v>189</v>
+      </c>
+      <c r="O47" t="s">
+        <v>45</v>
+      </c>
+      <c r="P47" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>47</v>
+      </c>
+      <c r="R47" t="s">
+        <v>48</v>
+      </c>
+      <c r="S47" t="s">
+        <v>268</v>
+      </c>
+      <c r="T47" t="s">
+        <v>272</v>
+      </c>
+      <c r="U47" t="s">
+        <v>257</v>
+      </c>
+      <c r="V47" t="s">
         <v>227</v>
       </c>
-      <c r="H47" t="s">
-        <v>155</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="W47" t="s">
+        <v>271</v>
+      </c>
+      <c r="X47" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC47" t="s">
         <v>195</v>
       </c>
-      <c r="J47" t="s">
-        <v>157</v>
-      </c>
-      <c r="K47" t="s">
-        <v>10</v>
-      </c>
-      <c r="L47" t="s">
-        <v>11</v>
-      </c>
-      <c r="M47" t="s">
-        <v>158</v>
-      </c>
-      <c r="N47" t="s">
-        <v>159</v>
-      </c>
-      <c r="O47" t="s">
-        <v>14</v>
-      </c>
-      <c r="P47" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>16</v>
-      </c>
-      <c r="R47" t="s">
-        <v>17</v>
-      </c>
-      <c r="S47" t="s">
-        <v>238</v>
-      </c>
-      <c r="T47" t="s">
-        <v>242</v>
-      </c>
-      <c r="U47" t="s">
-        <v>227</v>
-      </c>
-      <c r="V47" t="s">
-        <v>197</v>
-      </c>
-      <c r="W47" t="s">
-        <v>241</v>
-      </c>
-      <c r="X47" t="s">
-        <v>198</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA47" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB47" t="s">
+      <c r="AD47" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:32" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>273</v>
+      </c>
+      <c r="B48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" t="s">
+        <v>37</v>
+      </c>
+      <c r="G48" t="s">
+        <v>274</v>
+      </c>
+      <c r="H48" t="s">
+        <v>39</v>
+      </c>
+      <c r="I48" t="s">
+        <v>275</v>
+      </c>
+      <c r="J48" t="s">
+        <v>276</v>
+      </c>
+      <c r="K48" t="s">
+        <v>41</v>
+      </c>
+      <c r="L48" t="s">
         <v>42</v>
       </c>
-      <c r="AC47" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD47" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF47" t="s">
-        <v>24</v>
+      <c r="M48" t="s">
+        <v>43</v>
+      </c>
+      <c r="N48" t="s">
+        <v>44</v>
+      </c>
+      <c r="O48" t="s">
+        <v>45</v>
+      </c>
+      <c r="P48" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>47</v>
+      </c>
+      <c r="R48" t="s">
+        <v>48</v>
+      </c>
+      <c r="S48" t="s">
+        <v>49</v>
+      </c>
+      <c r="T48" t="s">
+        <v>275</v>
+      </c>
+      <c r="U48" t="s">
+        <v>274</v>
+      </c>
+      <c r="V48" t="s">
+        <v>275</v>
+      </c>
+      <c r="W48" t="s">
+        <v>35</v>
+      </c>
+      <c r="X48" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF47" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DBA420-F843-4D11-BCF7-56E4F777E424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DDC856-1637-4F31-BEC1-77E03DD7A982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DDC856-1637-4F31-BEC1-77E03DD7A982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8842401-F3A1-4583-A417-AA34407BFA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -896,7 +896,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -909,11 +909,19 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -969,7 +977,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -981,6 +989,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2063,31 +2077,31 @@
       </c>
     </row>
     <row r="9" spans="1:32" ht="26.25" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="3" t="s">
         <v>99</v>
       </c>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3666,11 +3666,7 @@
           <t>Periode tanggal 08 sd 31 Agustus 2026</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>025/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>31 Aug 2026</t>
@@ -3679,7 +3675,7 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -3716,7 +3712,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3862,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4012,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4162,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4312,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4462,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4612,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4762,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4912,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5070,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5228,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5386,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5544,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5702,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5860,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6018,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6176,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6334,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6492,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6650,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6808,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6966,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7124,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7282,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7440,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7598,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7756,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7914,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8072,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8230,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-19 18:15:02</t>
+          <t>2026-09-19 19:51:36</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3366,11 +3366,7 @@
           <t>Periode tanggal 8 sd 31 Agustus 2026</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>023/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>31 Aug 2026</t>
@@ -3379,7 +3375,7 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -3416,7 +3412,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3562,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3708,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3858,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4008,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4158,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4308,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4458,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4608,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4758,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4908,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5066,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5224,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5382,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5540,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5698,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5856,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6014,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6172,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6330,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6488,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6646,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6804,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6962,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7120,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7278,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7436,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7594,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7752,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7910,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8068,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8226,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8372,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-19 21:19:57</t>
+          <t>2026-09-20 06:40:32</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF52"/>
+  <dimension ref="A1:AF53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>03 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3216,11 +3216,7 @@
           <t>4 September 2026</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
-        </is>
-      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>04 Sep 2026</t>
@@ -3229,7 +3225,7 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -3266,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3558,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3704,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3854,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4004,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4154,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4304,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4454,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4604,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4754,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4904,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5062,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5220,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5378,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5536,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5694,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5852,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6010,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6168,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6326,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6484,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6642,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6800,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6958,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7116,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7274,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7432,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7590,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7748,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7906,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8064,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8222,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8368,153 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-20 06:40:32</t>
+          <t>2026-09-20 08:03:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Periode tanggal 8 sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:03:11</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3508,11 +3508,7 @@
           <t>Periode Tanggal 8 sd 31 Agustus 2026</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>024/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>31 Aug 2026</t>
@@ -3521,7 +3517,7 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>PSupporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -3558,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3850,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4000,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4150,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4300,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4450,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4600,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4750,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4900,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5058,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5216,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5374,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5532,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -5694,7 +5690,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5848,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6006,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6164,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6322,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6480,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6638,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6796,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6954,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7112,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7270,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7428,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7586,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7744,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7902,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8060,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8218,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8364,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8510,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-09-20 08:03:11</t>
+          <t>2026-09-20 09:07:45</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF53"/>
+  <dimension ref="A1:AF54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>06 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3800,11 +3800,7 @@
           <t>Periode tanggal 07 sd 31 Agustus 2026</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>026/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>31 Aug 2026</t>
@@ -3813,7 +3809,7 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -3850,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3868,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3897,12 +3893,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3950,11 +3946,7 @@
           <t>Periode tanggal 07 sd 31 Agustus 2026</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>31 Aug 2026</t>
@@ -3963,7 +3955,7 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -4000,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -5216,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -6006,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -7902,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8356,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8502,153 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-09-20 09:07:45</t>
+          <t>2026-09-20 10:44:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Periode Tanggal 8 sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>PSupporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:44:12</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-09-20 10:44:12</t>
+          <t>2026-09-20 13:10:51</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF54"/>
+  <dimension ref="A1:AF59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,743 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-09-20 13:10:51</t>
+          <t>2026-09-21 14:50:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
+Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Periode 08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
+Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:50:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>30 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Periode 08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>30 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:50:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Periode 08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:50:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:50:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:50:31</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Akomodasi penginapan crew Wellservices</t>
+          <t>Provsum Akomodasi penginapan crew Wellservices</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8319,7 +8319,7 @@
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Akomodasi penginapan crew Wellservices</t>
+          <t>Provsum Akomodasi penginapan crew Wellservices</t>
         </is>
       </c>
       <c r="X52" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-09-21 14:50:31</t>
+          <t>2026-09-22 08:18:02</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF59"/>
+  <dimension ref="A1:AF60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,153 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-09-22 08:18:02</t>
+          <t>2026-09-29 20:30:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>2026-09-29 20:30:07</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF60"/>
+  <dimension ref="A1:AF61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9195,13 +9195,13 @@
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -9238,14 +9238,14 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/IX/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -9335,19 +9335,19 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -9384,7 +9384,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,153 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-09-29 20:30:07</t>
+          <t>2026-10-01 13:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:16:59</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF61"/>
+  <dimension ref="A1:AF62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8648,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9384,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,153 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-01 13:16:59</t>
+          <t>2026-10-01 23:02:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>2026-10-01 23:02:30</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi penginapan crew Wellservices</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -8255,11 +8255,7 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>03 Aug 2026</t>
@@ -8319,7 +8315,7 @@
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi penginapan crew Wellservices</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
         </is>
       </c>
       <c r="X52" t="inlineStr"/>
@@ -8356,7 +8352,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8498,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -8648,7 +8644,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8794,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8942,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9088,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9234,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9380,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9402,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -9421,7 +9417,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9431,12 +9427,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -9481,19 +9477,19 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -9530,7 +9526,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9672,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9818,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-01 23:02:30</t>
+          <t>2026-10-02 09:31:09</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>04 September 2026</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2929,7 +2929,7 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -9234,7 +9234,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9672,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-02 09:31:09</t>
+          <t>2026-10-03 12:06:31</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -9635,7 +9635,7 @@
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -9672,7 +9672,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-03 12:06:31</t>
+          <t>2026-10-05 09:07:46</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF62"/>
+  <dimension ref="A1:AF69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5208,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8498,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
@@ -9672,14 +9672,14 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -9769,19 +9769,19 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>Periode tanggal 01 sd 30 September 2026</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>30 Sep 2026</t>
         </is>
       </c>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
@@ -9818,7 +9818,1031 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-05 09:07:46</t>
+          <t>2026-10-06 13:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Periode Tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Periode Tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>11 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Periode Bulan September 2026</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>11 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:11:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:11:45</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF69"/>
+  <dimension ref="A1:AF73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -4037,11 +4037,7 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>45000000test</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>07 Aug 2026</t>
@@ -4142,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -10402,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>
@@ -10842,7 +10838,583 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-06 13:11:45</t>
+          <t>2026-10-06 19:56:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Additional Camp dan Heavy Trasportation dan  Equipment  Rental Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Additional Camp dan Heavy Trasportation dan  Equipment  Rental Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:56:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>048/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:56:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode September 2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>01 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode September 2026</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:56:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>050/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode bulan September 2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>01 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode bulan September 2026</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:56:22</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-10-06 19:56:22</t>
+          <t>2026-10-07 05:58:51</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF73"/>
+  <dimension ref="A1:AF77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,581 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-10-07 05:58:51</t>
+          <t>2026-10-07 10:53:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Periode 08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:53:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Periode 08 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>08 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:53:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Land Transportation ( Moving  equipment rental antar well ) Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Periode 14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Land Transportation ( Moving  equipment rental antar well ) Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:53:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Land Transportation ( Moving  equipment rental antar well ) Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>20 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>20 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Land Transportation ( Moving  equipment rental antar well ) Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:53:54</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF77"/>
+  <dimension ref="A1:AF78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11704,7 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,149 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>2026-10-07 10:53:54</t>
+          <t>2026-10-07 11:13:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base dan Land Transportation</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Periode 23 sd 29  Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base dan Land Transportation</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:13:53</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF78"/>
+  <dimension ref="A1:AF80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11704,7 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,291 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>2026-10-07 11:13:53</t>
+          <t>2026-10-13 10:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:25:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>052/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>15 September 2026</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:25:01</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B (Garam, Belerang)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2312,11 +2312,7 @@
           <t>17 Januari 2026</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
           <t>30 Jan 2026</t>
@@ -2325,7 +2321,7 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B (Garam, Belerang)</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -2362,7 +2358,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2508,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2662,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2812,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2962,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2984,9 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
+          <t>PROVISIONAL SUM
+Kontainer box untuk penyimpanan perlatan pendukung (ATK,
+APD, Dokumen, dll)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3013,12 +3011,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>03 Sep 2026</t>
+          <t>01 Sep 2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3079,7 +3077,9 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
+          <t>PROVISIONAL SUM
+Kontainer box untuk penyimpanan perlatan pendukung (ATK,
+APD, Dokumen, dll)</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11704,7 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12414,7 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>2026-10-13 10:25:01</t>
+          <t>2026-10-14 13:51:56</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1733,7 +1733,7 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -10398,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11704,7 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12414,7 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>2026-10-14 13:51:56</t>
+          <t>2026-10-15 17:43:10</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -732,7 +732,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -878,7 +878,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1178,7 +1178,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1478,7 +1478,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1624,7 +1624,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1920,7 +1920,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2070,7 +2070,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2358,7 +2358,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Logistic tambahan kegiatan Well Services Agustus 2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2465,13 +2465,13 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Logistic tambahan kegiatan Well Services Agustus 2026</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -2508,7 +2508,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2662,7 +2662,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Logistic tambahan kegiatan Well Services September 2026.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011844</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2925,7 +2925,7 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Logistic tambahan kegiatan Well Services September 2026.</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3262,7 +3262,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3408,7 +3408,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3554,7 +3554,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3700,7 +3700,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3846,7 +3846,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3992,7 +3992,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4288,7 +4288,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4588,7 +4588,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4738,7 +4738,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4888,7 +4888,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6942,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -8348,7 +8348,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -8494,7 +8494,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -8640,7 +8640,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -8790,7 +8790,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -8938,7 +8938,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -9084,7 +9084,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Logistic tambahan II kegiatan Well Services September 2026.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011849</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -9193,7 +9193,7 @@
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Logistic tambahan II kegiatan Well Services September 2026.</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -9230,7 +9230,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -9376,7 +9376,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -9522,7 +9522,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Logistic tambahan III kegiatan Well Services September 2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -9564,17 +9564,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011850</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>26 Sep 2026</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -9631,7 +9631,7 @@
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Logistic tambahan III kegiatan Well Services September 2026</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -9668,7 +9668,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -9814,7 +9814,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -9960,7 +9960,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -10106,7 +10106,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -10252,7 +10252,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -10398,7 +10398,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -10546,7 +10546,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -10692,7 +10692,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -10734,7 +10734,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -10838,7 +10838,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -10984,7 +10984,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -11130,7 +11130,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -11272,7 +11272,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -11562,7 +11562,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -11988,7 +11988,7 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -12130,7 +12130,7 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -12272,7 +12272,7 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiatan Pengeboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>2026-10-15 17:43:10</t>
+          <t>2026-10-16 11:28:16</t>
         </is>
       </c>
     </row>
